--- a/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CAA122A-A426-4C47-BFA8-F252521CA920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583B3B8A-9180-4ED9-9568-2B13A1FE8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M3" s="2">
         <v>62.984000000000002</v>
@@ -898,7 +898,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
       <c r="L4" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -986,7 +986,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="L5" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M5" s="2">
         <v>53.112000000000002</v>
@@ -1072,7 +1072,7 @@
         <v>0.05</v>
       </c>
       <c r="L6" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M6" s="2">
         <v>43.322000000000003</v>
@@ -1158,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M7" s="7">
         <f>293.323/30</f>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2">
-        <v>0</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M9" s="7">
         <f>357.554/30</f>
@@ -1431,8 +1431,8 @@
       <c r="K10">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="L10">
-        <v>0</v>
+      <c r="L10" s="2">
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="M10" s="2">
         <v>0</v>
@@ -1515,7 +1515,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 U3:V9 S4:T4 T4:T7 A10:L10 A11:XFD1048576">
+  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 U3:V9 S4:T4 T4:T7 A10:K10 A11:XFD1048576">
     <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{583B3B8A-9180-4ED9-9568-2B13A1FE8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEF25F-15DA-4E21-A217-168A5C1983A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>name</t>
   </si>
@@ -160,12 +160,6 @@
   </si>
   <si>
     <t>price_sigma</t>
-  </si>
-  <si>
-    <t>CO2km_min</t>
-  </si>
-  <si>
-    <t>CO2km_max</t>
   </si>
   <si>
     <t>CS_electric</t>
@@ -175,27 +169,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -210,13 +187,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,85 +210,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -587,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB18"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
@@ -598,106 +505,99 @@
     <col min="10" max="10" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="7.88671875" customWidth="1"/>
     <col min="13" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="11.109375" style="5" customWidth="1"/>
+    <col min="17" max="18" width="11.109375" customWidth="1"/>
     <col min="19" max="19" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.6640625" customWidth="1"/>
-    <col min="23" max="23" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" customWidth="1"/>
-    <col min="25" max="25" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>4</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>5</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="W1" t="s">
         <v>11</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="X1" t="s">
         <v>12</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>13</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -722,10 +622,10 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2" s="11">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M2">
@@ -734,34 +634,34 @@
       <c r="N2">
         <v>0</v>
       </c>
-      <c r="O2" s="13">
-        <v>0</v>
-      </c>
-      <c r="P2" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="5">
-        <v>0</v>
-      </c>
-      <c r="R2" s="5">
-        <v>0</v>
-      </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
-        <v>0</v>
-      </c>
-      <c r="U2" s="8">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W2" s="12">
-        <v>0</v>
-      </c>
-      <c r="X2" s="12">
+      <c r="O2" s="1">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2">
@@ -770,14 +670,8 @@
       <c r="Z2">
         <v>0</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -796,10 +690,10 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
       <c r="I3">
@@ -808,47 +702,47 @@
       <c r="J3">
         <v>0.1</v>
       </c>
-      <c r="K3" s="11">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="L3" s="2">
+      <c r="K3" s="1">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="L3">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3">
         <v>62.984000000000002</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3">
         <v>2.94</v>
       </c>
-      <c r="O3" s="11">
-        <v>1.3420000000000001</v>
-      </c>
-      <c r="P3" s="11">
-        <v>1.2190000000000001</v>
-      </c>
-      <c r="Q3" s="6">
+      <c r="O3" s="1">
+        <v>2.6709999999999998</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="Q3" s="1">
         <v>9999</v>
       </c>
-      <c r="R3" s="5">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
-        <v>0</v>
-      </c>
-      <c r="V3" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W3" s="12">
-        <v>85.105000000000004</v>
-      </c>
-      <c r="X3" s="12">
-        <v>79.673000000000002</v>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3" s="1">
+        <v>177.70699999999999</v>
+      </c>
+      <c r="V3" s="1">
+        <v>14.922000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
       </c>
       <c r="Y3">
         <v>0</v>
@@ -856,14 +750,8 @@
       <c r="Z3">
         <v>0</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -882,10 +770,10 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
       <c r="I4">
@@ -894,10 +782,10 @@
       <c r="J4">
         <v>0.1</v>
       </c>
-      <c r="K4" s="11">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L4" s="2">
+      <c r="K4" s="1">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="L4">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M4">
@@ -906,52 +794,46 @@
       <c r="N4">
         <v>0</v>
       </c>
-      <c r="O4" s="11">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="P4" s="11">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="Q4" s="6">
+      <c r="O4" s="1">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="P4" s="1">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="Q4" s="1">
         <v>9999</v>
       </c>
-      <c r="R4" s="5">
-        <v>0</v>
-      </c>
-      <c r="S4" s="9">
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4">
         <f>O4*0.5</f>
-        <v>0.214</v>
-      </c>
-      <c r="T4" s="9">
+        <v>0.41949999999999998</v>
+      </c>
+      <c r="T4">
         <f>P4*0.5</f>
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="U4" s="8">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W4" s="12">
-        <v>0</v>
-      </c>
-      <c r="X4" s="12">
-        <v>0</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>80</v>
+      </c>
+      <c r="X4">
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Z4">
-        <v>10</v>
-      </c>
-      <c r="AA4">
-        <v>60</v>
-      </c>
-      <c r="AB4">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -970,10 +852,10 @@
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
       <c r="I5">
@@ -982,47 +864,47 @@
       <c r="J5">
         <v>0.1</v>
       </c>
-      <c r="K5" s="11">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="K5" s="1">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="L5">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <v>53.112000000000002</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5">
         <v>3.9049999999999998</v>
       </c>
-      <c r="O5" s="11">
-        <v>1.0920000000000001</v>
-      </c>
-      <c r="P5" s="11">
-        <v>1.0780000000000001</v>
-      </c>
-      <c r="Q5" s="6">
+      <c r="O5" s="1">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="Q5" s="1">
         <v>9999</v>
       </c>
-      <c r="R5" s="5">
-        <v>0</v>
-      </c>
-      <c r="S5" s="8">
-        <v>0</v>
-      </c>
-      <c r="T5" s="8">
-        <v>0</v>
-      </c>
-      <c r="U5" s="8">
-        <v>0</v>
-      </c>
-      <c r="V5" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W5" s="12">
-        <v>75.765000000000001</v>
-      </c>
-      <c r="X5" s="12">
-        <v>74.77</v>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1">
+        <v>146.732</v>
+      </c>
+      <c r="V5" s="1">
+        <v>20.474</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
       </c>
       <c r="Y5">
         <v>0</v>
@@ -1030,14 +912,8 @@
       <c r="Z5">
         <v>0</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1056,10 +932,10 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6">
@@ -1068,47 +944,47 @@
       <c r="J6">
         <v>0.1</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <v>43.322000000000003</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6">
         <v>2.206</v>
       </c>
-      <c r="O6" s="11">
-        <v>0.94199999999999995</v>
-      </c>
-      <c r="P6" s="11">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="Q6" s="6">
+      <c r="O6" s="1">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="Q6" s="1">
         <v>9999</v>
       </c>
-      <c r="R6" s="5">
-        <v>0</v>
-      </c>
-      <c r="S6" s="8">
-        <v>0</v>
-      </c>
-      <c r="T6" s="8">
-        <v>0</v>
-      </c>
-      <c r="U6" s="8">
-        <v>0</v>
-      </c>
-      <c r="V6" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W6" s="12">
-        <v>17.8</v>
-      </c>
-      <c r="X6" s="12">
-        <v>39.914999999999999</v>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1">
+        <v>37.835000000000001</v>
+      </c>
+      <c r="V6" s="1">
+        <v>60.267000000000003</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
       </c>
       <c r="Y6">
         <v>0</v>
@@ -1116,14 +992,8 @@
       <c r="Z6">
         <v>0</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1142,10 +1012,10 @@
       <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
       <c r="I7">
@@ -1154,53 +1024,54 @@
       <c r="J7">
         <v>0.1</v>
       </c>
-      <c r="K7" s="11">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="K7" s="1">
+        <f>4/21*0</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7">
         <f>293.323/30</f>
         <v>9.7774333333333328</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7">
         <f>38.284/30</f>
         <v>1.2761333333333333</v>
       </c>
-      <c r="O7" s="14">
-        <f>5.45/30</f>
-        <v>0.18166666666666667</v>
-      </c>
-      <c r="P7" s="14">
-        <f>5.317/30</f>
-        <v>0.17723333333333333</v>
-      </c>
-      <c r="Q7" s="6">
+      <c r="O7" s="2">
+        <f>12.372/45</f>
+        <v>0.27493333333333331</v>
+      </c>
+      <c r="P7" s="2">
+        <f>1.668/45</f>
+        <v>3.7066666666666664E-2</v>
+      </c>
+      <c r="Q7" s="1">
         <v>9999</v>
       </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W7" s="12">
-        <f>310.302/30</f>
-        <v>10.343400000000001</v>
-      </c>
-      <c r="X7" s="12">
-        <f>342.664/30</f>
-        <v>11.422133333333333</v>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2">
+        <f>740.509/45</f>
+        <v>16.455755555555555</v>
+      </c>
+      <c r="V7" s="2">
+        <f>271.113/45</f>
+        <v>6.0247333333333337</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -1208,14 +1079,8 @@
       <c r="Z7">
         <v>0</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>29</v>
       </c>
@@ -1234,10 +1099,10 @@
       <c r="F8">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" t="s">
         <v>37</v>
       </c>
       <c r="I8">
@@ -1246,10 +1111,11 @@
       <c r="J8">
         <v>0.1</v>
       </c>
-      <c r="K8" s="11">
-        <v>0</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="K8" s="1">
+        <f t="shared" ref="K8:K9" si="0">4/21*0</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="M8">
@@ -1258,54 +1124,48 @@
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8" s="11">
-        <f>2.883/30</f>
-        <v>9.6100000000000005E-2</v>
-      </c>
-      <c r="P8" s="11">
-        <f>2.742/30</f>
-        <v>9.1399999999999995E-2</v>
-      </c>
-      <c r="Q8" s="6">
+      <c r="O8" s="2">
+        <f>5.542/45</f>
+        <v>0.12315555555555555</v>
+      </c>
+      <c r="P8" s="2">
+        <f>1.704/45</f>
+        <v>3.7866666666666667E-2</v>
+      </c>
+      <c r="Q8" s="1">
         <v>9999</v>
       </c>
-      <c r="R8" s="5">
-        <v>0</v>
-      </c>
-      <c r="S8" s="9">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8">
         <f>O8*0.5</f>
-        <v>4.8050000000000002E-2</v>
-      </c>
-      <c r="T8" s="9">
+        <v>6.1577777777777773E-2</v>
+      </c>
+      <c r="T8">
         <f>P8*0.5</f>
-        <v>4.5699999999999998E-2</v>
-      </c>
-      <c r="U8" s="8">
-        <v>0</v>
-      </c>
-      <c r="V8" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W8" s="12">
-        <v>0</v>
-      </c>
-      <c r="X8" s="12">
-        <v>0</v>
+        <v>1.8933333333333333E-2</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>80</v>
+      </c>
+      <c r="X8">
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Z8">
-        <v>10</v>
-      </c>
-      <c r="AA8">
-        <v>60</v>
-      </c>
-      <c r="AB8">
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1324,10 +1184,10 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>35</v>
       </c>
       <c r="I9">
@@ -1336,53 +1196,50 @@
       <c r="J9">
         <v>0.1</v>
       </c>
-      <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="K9" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L9">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9">
         <f>357.554/30</f>
         <v>11.918466666666665</v>
       </c>
-      <c r="N9" s="7">
+      <c r="N9">
         <f>68.396/30</f>
         <v>2.2798666666666665</v>
       </c>
-      <c r="O9" s="14">
-        <f>8.398/30</f>
-        <v>0.27993333333333331</v>
-      </c>
-      <c r="P9" s="14">
-        <f>8.473/30</f>
-        <v>0.28243333333333337</v>
-      </c>
-      <c r="Q9" s="6">
+      <c r="O9" s="1">
+        <v>16.117999999999999</v>
+      </c>
+      <c r="P9" s="1">
+        <v>2.637</v>
+      </c>
+      <c r="Q9" s="1">
         <v>9999</v>
       </c>
-      <c r="R9" s="5">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
-        <v>0</v>
-      </c>
-      <c r="V9" s="8">
-        <v>999999</v>
-      </c>
-      <c r="W9" s="12">
-        <f>102.678/30</f>
-        <v>3.4226000000000001</v>
-      </c>
-      <c r="X9" s="12">
-        <f>196.822/30</f>
-        <v>6.5607333333333333</v>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1">
+        <v>411.62700000000001</v>
+      </c>
+      <c r="V9" s="1">
+        <v>386.86799999999999</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -1390,16 +1247,10 @@
       <c r="Z9">
         <v>0</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -1428,133 +1279,56 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10">
-        <v>9.7000000000000003E-2</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="K10" s="1">
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="L10">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="M10" s="2">
-        <v>0</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>0.42799999999999999</v>
-      </c>
-      <c r="P10" s="2">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="Q10" s="2">
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="P10" s="1">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="Q10" s="1">
         <v>9999</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="1">
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0.214</v>
+        <v>0.41949999999999998</v>
       </c>
       <c r="T10">
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>999999</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1">
+        <v>0</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Z10">
-        <v>10</v>
-      </c>
-      <c r="AA10">
-        <v>60</v>
-      </c>
-      <c r="AB10">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q11"/>
-      <c r="R11"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q12"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q13"/>
-      <c r="R13"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q14"/>
-      <c r="R14"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q15"/>
-      <c r="R15"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="Q16"/>
-      <c r="R16"/>
-    </row>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <conditionalFormatting sqref="A7:J9">
-    <cfRule type="cellIs" dxfId="8" priority="17" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:XFD1 A1:I6 M2:XFD2 J2:J6 U3:V9 S4:T4 T4:T7 A10:K10 A11:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="22" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M4:P4">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M7:P8">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:T3">
-    <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:R10">
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S7">
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S8:T9 S10:V10">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W3:XFD10">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
+++ b/data/s4/Aradas/archetypes/pop_archetypes_transport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s4\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CEF25F-15DA-4E21-A217-168A5C1983A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A138E21B-6A8B-4D28-A8CD-33B26DA3BDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="855" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,6 +197,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -210,10 +216,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1279,8 +1286,8 @@
       <c r="J10">
         <v>0.1</v>
       </c>
-      <c r="K10" s="1">
-        <v>7.6300000000000007E-2</v>
+      <c r="K10" s="3">
+        <v>0.34335367396867361</v>
       </c>
       <c r="L10">
         <v>1.0000000000000001E-5</v>
